--- a/sample/b.xlsx
+++ b/sample/b.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t xml:space="preserve">索引</t>
   </si>
@@ -32,6 +32,12 @@
     <t xml:space="preserve">說明</t>
   </si>
   <si>
+    <t xml:space="preserve">字符串列表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">字典</t>
+  </si>
+  <si>
     <t xml:space="preserve">數量</t>
   </si>
   <si>
@@ -41,6 +47,12 @@
     <t xml:space="preserve">str</t>
   </si>
   <si>
+    <t xml:space="preserve">strlist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dict</t>
+  </si>
+  <si>
     <t xml:space="preserve">#</t>
   </si>
   <si>
@@ -53,6 +65,12 @@
     <t xml:space="preserve">tip</t>
   </si>
   <si>
+    <t xml:space="preserve">namedb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dicv</t>
+  </si>
+  <si>
     <t xml:space="preserve">__count</t>
   </si>
   <si>
@@ -63,6 +81,12 @@
   </si>
   <si>
     <t xml:space="preserve">to kill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint,Cursed,Healing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"ATK": 100</t>
   </si>
   <si>
     <t xml:space="preserve">water</t>
@@ -151,7 +175,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -161,10 +185,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -357,7 +377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -373,46 +393,64 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>4</v>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -420,27 +458,35 @@
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -475,13 +521,13 @@
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I5" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
